--- a/Data/FactorInformation.xlsx
+++ b/Data/FactorInformation.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ander\Documents\Internship-project\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ander\Desktop\Git_project\Internship-project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992BA0AA-B411-4A36-9F9D-555B7B6C90D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F043F6-A3AB-41AF-AC23-18E1906F030D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{31F7844C-8DE3-4AF0-9DCF-66B216B51E59}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{31F7844C-8DE3-4AF0-9DCF-66B216B51E59}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -511,13 +511,13 @@
     <t>zero_trades_252d</t>
   </si>
   <si>
-    <t>release date</t>
-  </si>
-  <si>
-    <t>original sample start</t>
-  </si>
-  <si>
-    <t>original sample end</t>
+    <t>releasedate</t>
+  </si>
+  <si>
+    <t>originalsamplestart</t>
+  </si>
+  <si>
+    <t>originalsampleend</t>
   </si>
 </sst>
 </file>
@@ -890,15 +890,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814FBD79-1E74-4D1B-9857-37F924E15E1F}">
   <dimension ref="A1:D154"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.15625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.83984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.15625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -912,7 +912,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -926,7 +926,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -940,7 +940,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -954,7 +954,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -968,7 +968,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -982,7 +982,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -996,7 +996,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1024,7 +1024,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1038,7 +1038,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1108,7 +1108,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -1150,7 +1150,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>28</v>
       </c>
@@ -1301,7 +1301,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>29</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>31</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>32</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>33</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>35</v>
       </c>
@@ -1399,7 +1399,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>36</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>37</v>
       </c>
@@ -1427,7 +1427,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>38</v>
       </c>
@@ -1441,7 +1441,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>41</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>42</v>
       </c>
@@ -1497,7 +1497,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>43</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -1525,7 +1525,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>45</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>48</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>49</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>50</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>51</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>52</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>53</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>55</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>56</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>57</v>
       </c>
@@ -1701,7 +1701,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>58</v>
       </c>
@@ -1715,7 +1715,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>60</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>61</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>62</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>64</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>65</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>66</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>67</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>68</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>70</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>71</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>72</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>73</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -1944,7 +1944,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -2064,7 +2064,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -2176,7 +2176,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>98</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>99</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>100</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>101</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>102</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>103</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>104</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>105</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>106</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>107</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>108</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>109</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>110</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>111</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>112</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>113</v>
       </c>
@@ -2464,7 +2464,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>114</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>116</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>117</v>
       </c>
@@ -2520,7 +2520,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>118</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>119</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>120</v>
       </c>
@@ -2562,7 +2562,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>121</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>122</v>
       </c>
@@ -2590,7 +2590,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>123</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>124</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>125</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>126</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>127</v>
       </c>
@@ -2660,7 +2660,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>128</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>129</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>131</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>132</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>133</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>134</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>135</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>136</v>
       </c>
@@ -2783,7 +2783,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>137</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>138</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>139</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -2839,7 +2839,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>141</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>142</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>143</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>144</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>145</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>146</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>147</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>148</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>149</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>150</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>151</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>152</v>
       </c>
@@ -3007,7 +3007,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>153</v>
       </c>
